--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A9BDC8-2079-45FC-B2B2-6651F0B10B18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44EBA45-E627-4050-8A06-3EC7000D38A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="28" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="89">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -323,6 +323,42 @@
   </si>
   <si>
     <t>DATE ___________03/09/2026___________</t>
+  </si>
+  <si>
+    <t>6/5b</t>
+  </si>
+  <si>
+    <t>6/23b</t>
+  </si>
+  <si>
+    <t>13/4b</t>
+  </si>
+  <si>
+    <t>2/12b</t>
+  </si>
+  <si>
+    <t>12b</t>
+  </si>
+  <si>
+    <t>9/3b</t>
+  </si>
+  <si>
+    <t>10/12b</t>
+  </si>
+  <si>
+    <t>1/12b</t>
+  </si>
+  <si>
+    <t>3/4b</t>
+  </si>
+  <si>
+    <t>12/8b</t>
+  </si>
+  <si>
+    <t>5/20b</t>
+  </si>
+  <si>
+    <t>18/4b</t>
   </si>
 </sst>
 </file>
@@ -1202,15 +1238,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1220,22 +1247,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3062,40 +3098,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -3103,7 +3139,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -3335,12 +3371,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -4667,40 +4703,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -4708,7 +4744,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -4940,12 +4976,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -4981,17 +5017,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6290,40 +6326,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -6331,7 +6367,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -6563,12 +6599,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -6604,17 +6640,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7913,40 +7949,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -7954,7 +7990,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -8186,12 +8222,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -8227,17 +8263,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9534,40 +9570,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -9575,7 +9611,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -9807,12 +9843,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -11139,40 +11175,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -11180,7 +11216,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -11412,12 +11448,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -11453,17 +11489,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12762,40 +12798,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -12803,7 +12839,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -13035,12 +13071,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -13076,17 +13112,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14385,40 +14421,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -14426,7 +14462,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -14658,12 +14694,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -14699,17 +14735,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16006,40 +16042,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -16047,7 +16083,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -16279,12 +16315,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -17611,40 +17647,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -17652,7 +17688,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -17884,12 +17920,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -17925,17 +17961,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19232,40 +19268,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -19273,7 +19309,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -19505,12 +19541,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -20837,40 +20873,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -20878,7 +20914,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -21110,12 +21146,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -21151,17 +21187,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -22460,40 +22496,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -22501,7 +22537,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -22733,12 +22769,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -22774,17 +22810,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -24081,40 +24117,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -24122,7 +24158,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -24354,12 +24390,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -25686,40 +25722,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -25727,7 +25763,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -25959,12 +25995,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -26000,17 +26036,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -27309,40 +27345,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -27350,7 +27386,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -27582,12 +27618,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -27623,17 +27659,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28932,40 +28968,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -28973,7 +29009,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -29205,12 +29241,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -29246,17 +29282,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30553,40 +30589,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -30594,7 +30630,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -30826,12 +30862,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -32158,40 +32194,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -32199,7 +32235,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -32431,12 +32467,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -32472,17 +32508,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -33781,40 +33817,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -33822,7 +33858,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -34054,12 +34090,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -34095,17 +34131,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35404,40 +35440,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -35445,7 +35481,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -35677,12 +35713,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -35718,17 +35754,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -36125,12 +36161,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -36140,12 +36184,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="60"/>
       <c r="Y8" s="15"/>
     </row>
@@ -36313,12 +36363,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -36328,12 +36386,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>2</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="62"/>
       <c r="Y15" s="24"/>
     </row>
@@ -36341,12 +36405,20 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="59"/>
+      <c r="C16" s="58">
+        <v>1</v>
+      </c>
+      <c r="D16" s="59">
+        <v>1</v>
+      </c>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>77</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -36356,12 +36428,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>2</v>
+      </c>
       <c r="X16" s="63"/>
       <c r="Y16" s="29"/>
     </row>
@@ -36765,17 +36843,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>19</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>12</v>
+      </c>
+      <c r="M24" s="14">
+        <v>325</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>5</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -36951,17 +37041,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>17</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>5</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -36979,17 +37081,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>18</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>12</v>
+      </c>
+      <c r="M32" s="28">
+        <v>308</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -37027,40 +37141,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -37068,7 +37182,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -37127,21 +37241,49 @@
       <c r="B36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
+      <c r="C36" s="47">
+        <v>1</v>
+      </c>
+      <c r="D36" s="42">
+        <v>1</v>
+      </c>
+      <c r="E36" s="43">
+        <v>20</v>
+      </c>
+      <c r="F36" s="43">
+        <v>240</v>
+      </c>
+      <c r="G36" s="43">
+        <v>1</v>
+      </c>
+      <c r="H36" s="43">
+        <v>1</v>
+      </c>
+      <c r="I36" s="43">
+        <v>22</v>
+      </c>
+      <c r="J36" s="43">
+        <v>1</v>
+      </c>
+      <c r="K36" s="43">
+        <v>7</v>
+      </c>
+      <c r="L36" s="43">
+        <v>3</v>
+      </c>
+      <c r="M36" s="43">
+        <v>2</v>
+      </c>
+      <c r="N36" s="43">
+        <v>11</v>
+      </c>
+      <c r="O36" s="43">
+        <v>7</v>
+      </c>
       <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="Q36" s="44">
+        <v>3</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -37285,27 +37427,55 @@
       <c r="B42" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="47"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
+      <c r="C42" s="47">
+        <v>1</v>
+      </c>
+      <c r="D42" s="42">
+        <v>1</v>
+      </c>
+      <c r="E42" s="43">
+        <v>20</v>
+      </c>
+      <c r="F42" s="43">
+        <v>240</v>
+      </c>
+      <c r="G42" s="43">
+        <v>1</v>
+      </c>
+      <c r="H42" s="43">
+        <v>1</v>
+      </c>
+      <c r="I42" s="43">
+        <v>22</v>
+      </c>
+      <c r="J42" s="43">
+        <v>1</v>
+      </c>
+      <c r="K42" s="43">
+        <v>7</v>
+      </c>
+      <c r="L42" s="43">
+        <v>3</v>
+      </c>
+      <c r="M42" s="43">
+        <v>2</v>
+      </c>
+      <c r="N42" s="43">
+        <v>11</v>
+      </c>
+      <c r="O42" s="43">
+        <v>7</v>
+      </c>
       <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="Q42" s="44">
+        <v>3</v>
+      </c>
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -37341,17 +37511,23 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95">
+        <f>1+1+1+6+2+2+18+1+12+308</f>
+        <v>352</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -37379,7 +37555,9 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.7109375" style="2" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -37748,12 +37926,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -37763,14 +37947,20 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>1</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -37936,12 +38126,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -37951,25 +38147,37 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>1</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>82</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -37979,14 +38187,20 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>0</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -38385,20 +38599,34 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>40</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>391</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -38571,20 +38799,34 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>9</v>
+      </c>
+      <c r="M31" s="23">
+        <v>40</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>85</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -38599,20 +38841,34 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>1</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27" t="s">
+        <v>83</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>40</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="L32" s="28">
+        <v>1</v>
+      </c>
+      <c r="M32" s="28">
+        <v>351</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -38650,40 +38906,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -38691,7 +38947,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -38750,21 +39006,45 @@
       <c r="B36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="47"/>
+      <c r="C36" s="47">
+        <v>9</v>
+      </c>
       <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
+      <c r="E36" s="43">
+        <v>10</v>
+      </c>
+      <c r="F36" s="43">
+        <v>465</v>
+      </c>
+      <c r="G36" s="43">
+        <v>10</v>
+      </c>
+      <c r="H36" s="43">
+        <v>5</v>
+      </c>
+      <c r="I36" s="43">
+        <v>1</v>
+      </c>
       <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
+      <c r="K36" s="43">
+        <v>2</v>
+      </c>
       <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="M36" s="43">
+        <v>1</v>
+      </c>
+      <c r="N36" s="43">
+        <v>36</v>
+      </c>
+      <c r="O36" s="43">
+        <v>6</v>
+      </c>
+      <c r="P36" s="43">
+        <v>22</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>5</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -38908,27 +39188,51 @@
       <c r="B42" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="47"/>
+      <c r="C42" s="47">
+        <v>9</v>
+      </c>
       <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
+      <c r="E42" s="43">
+        <v>10</v>
+      </c>
+      <c r="F42" s="43">
+        <v>465</v>
+      </c>
+      <c r="G42" s="43">
+        <v>10</v>
+      </c>
+      <c r="H42" s="43">
+        <v>5</v>
+      </c>
+      <c r="I42" s="43">
+        <v>1</v>
+      </c>
       <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
+      <c r="K42" s="43">
+        <v>2</v>
+      </c>
       <c r="L42" s="43"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="M42" s="43">
+        <v>1</v>
+      </c>
+      <c r="N42" s="43">
+        <v>36</v>
+      </c>
+      <c r="O42" s="43">
+        <v>6</v>
+      </c>
+      <c r="P42" s="43">
+        <v>22</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>5</v>
+      </c>
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -38964,17 +39268,23 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95">
+        <f>2+9+1+10+40+1+351</f>
+        <v>414</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95">
+        <f>3+12</f>
+        <v>15</v>
+      </c>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -39371,12 +39681,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>88</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -39386,14 +39700,20 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -39559,12 +39879,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>2</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>87</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -39574,25 +39898,35 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>2</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>86</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -39602,14 +39936,20 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>2</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -40011,23 +40351,37 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>111</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>15</v>
+      </c>
+      <c r="M24" s="14">
+        <v>421</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -40197,23 +40551,37 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>54</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>6</v>
+      </c>
+      <c r="M31" s="23">
+        <v>155</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>0</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="62"/>
       <c r="Y31" s="24"/>
@@ -40225,23 +40593,37 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>57</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>9</v>
+      </c>
+      <c r="M32" s="28">
+        <v>266</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>1</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="64"/>
       <c r="Y32" s="29"/>
@@ -40273,40 +40655,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -40314,7 +40696,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -40374,20 +40756,42 @@
         <v>52</v>
       </c>
       <c r="C36" s="47"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
+      <c r="D36" s="42">
+        <v>1</v>
+      </c>
+      <c r="E36" s="43">
+        <v>12</v>
+      </c>
+      <c r="F36" s="43">
+        <v>284</v>
+      </c>
+      <c r="G36" s="43">
+        <v>17</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
+      <c r="I36" s="43">
+        <v>16</v>
+      </c>
+      <c r="J36" s="43">
+        <v>1</v>
+      </c>
+      <c r="K36" s="43">
+        <v>10</v>
+      </c>
+      <c r="L36" s="43">
+        <v>2</v>
+      </c>
       <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
+      <c r="N36" s="43">
+        <v>10</v>
+      </c>
+      <c r="O36" s="43">
+        <v>12</v>
+      </c>
       <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="Q36" s="44">
+        <v>1</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -40532,26 +40936,48 @@
         <v>53</v>
       </c>
       <c r="C42" s="47"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
+      <c r="D42" s="42">
+        <v>1</v>
+      </c>
+      <c r="E42" s="43">
+        <v>12</v>
+      </c>
+      <c r="F42" s="43">
+        <v>284</v>
+      </c>
+      <c r="G42" s="43">
+        <v>17</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
+      <c r="I42" s="43">
+        <v>16</v>
+      </c>
+      <c r="J42" s="43">
+        <v>1</v>
+      </c>
+      <c r="K42" s="43">
+        <v>10</v>
+      </c>
+      <c r="L42" s="43">
+        <v>2</v>
+      </c>
       <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
+      <c r="N42" s="43">
+        <v>10</v>
+      </c>
+      <c r="O42" s="43">
+        <v>12</v>
+      </c>
       <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="Q42" s="44">
+        <v>1</v>
+      </c>
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -40587,17 +41013,23 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95">
+        <f>12+2+1+57+9+266+1</f>
+        <v>348</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -41894,40 +42326,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -41935,7 +42367,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -42167,12 +42599,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -43499,40 +43931,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -43540,7 +43972,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -43772,12 +44204,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -43813,17 +44245,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -45122,40 +45554,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -45163,7 +45595,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -45395,12 +45827,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -45436,17 +45868,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -46745,40 +47177,40 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="90" t="s">
+      <c r="B34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="84" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="84" t="s">
+      <c r="G34" s="91"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="84" t="s">
+      <c r="J34" s="91"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="85"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="93" t="s">
+      <c r="M34" s="91"/>
+      <c r="N34" s="92"/>
+      <c r="O34" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="87" t="s">
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
-      <c r="U34" s="89"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="86"/>
       <c r="V34" s="70"/>
       <c r="W34" s="67"/>
       <c r="X34" s="67"/>
@@ -46786,7 +47218,7 @@
       <c r="Z34" s="80"/>
     </row>
     <row r="35" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="91"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="51" t="s">
         <v>49</v>
       </c>
@@ -47018,12 +47450,12 @@
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="94" t="s">
+      <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
-      <c r="U42" s="95"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="88"/>
+      <c r="U42" s="88"/>
       <c r="V42" s="67"/>
       <c r="W42" s="67"/>
       <c r="X42" s="67"/>
@@ -47059,17 +47491,17 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44EBA45-E627-4050-8A06-3EC7000D38A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9DC409-CBA8-4CD2-904F-DC6F6BF71F29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="99">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -359,6 +359,36 @@
   </si>
   <si>
     <t>18/4b</t>
+  </si>
+  <si>
+    <t>9B</t>
+  </si>
+  <si>
+    <t>11/14B</t>
+  </si>
+  <si>
+    <t>11/23B</t>
+  </si>
+  <si>
+    <t>1/12B</t>
+  </si>
+  <si>
+    <t>2/12B</t>
+  </si>
+  <si>
+    <t>7/14B</t>
+  </si>
+  <si>
+    <t>7/10B</t>
+  </si>
+  <si>
+    <t>3/4B</t>
+  </si>
+  <si>
+    <t>20/20B</t>
+  </si>
+  <si>
+    <t>5/20B</t>
   </si>
 </sst>
 </file>
@@ -42660,7 +42690,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -43029,12 +43060,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -43044,12 +43083,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="60"/>
       <c r="Y8" s="15"/>
     </row>
@@ -43217,12 +43262,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -43232,12 +43285,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>2</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>2</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="62"/>
       <c r="Y15" s="24"/>
     </row>
@@ -43245,12 +43304,20 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>89</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -43260,12 +43327,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>0</v>
+      </c>
       <c r="X16" s="63"/>
       <c r="Y16" s="29"/>
     </row>
@@ -43669,17 +43742,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>35</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>419</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>7</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -43855,17 +43938,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>92</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>4</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>3</v>
+      </c>
+      <c r="M31" s="23">
+        <v>37</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>4</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -43883,17 +43976,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>31</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>7</v>
+      </c>
+      <c r="M32" s="28">
+        <v>382</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>3</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -44034,18 +44137,30 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
+      <c r="F36" s="43">
+        <v>393</v>
+      </c>
+      <c r="G36" s="43">
+        <v>1</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
+      <c r="I36" s="43">
+        <v>5</v>
+      </c>
+      <c r="J36" s="43">
+        <v>1</v>
+      </c>
+      <c r="K36" s="43">
+        <v>2</v>
+      </c>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
       <c r="N36" s="43"/>
       <c r="O36" s="43"/>
       <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="Q36" s="44">
+        <v>8</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -44192,18 +44307,30 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
+      <c r="F42" s="43">
+        <v>393</v>
+      </c>
+      <c r="G42" s="43">
+        <v>1</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
+      <c r="I42" s="43">
+        <v>5</v>
+      </c>
+      <c r="J42" s="43">
+        <v>1</v>
+      </c>
+      <c r="K42" s="43">
+        <v>2</v>
+      </c>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
       <c r="N42" s="43"/>
       <c r="O42" s="43"/>
       <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="Q42" s="44">
+        <v>8</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -44245,7 +44372,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>1+1+31+7+382+3</f>
+        <v>425</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -44253,7 +44383,9 @@
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
+      <c r="C45" s="95">
+        <v>9</v>
+      </c>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
     </row>
@@ -44652,12 +44784,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>15</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -44667,14 +44807,20 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>1</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -44840,12 +44986,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22" t="s">
+        <v>93</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>95</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -44855,25 +45009,39 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>1</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>0</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>94</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -44883,14 +45051,20 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>0</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -45289,20 +45463,32 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>72</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>9</v>
+      </c>
+      <c r="M24" s="14">
+        <v>364</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -45475,20 +45661,32 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>7</v>
+      </c>
+      <c r="M31" s="23">
+        <v>140</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>96</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -45503,20 +45701,32 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>1</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>71</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>224</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -45657,18 +45867,32 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
+      <c r="F36" s="43">
+        <v>282</v>
+      </c>
+      <c r="G36" s="43">
+        <v>31</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
+      <c r="I36" s="43">
+        <v>6</v>
+      </c>
       <c r="J36" s="43"/>
       <c r="K36" s="43"/>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="N36" s="43">
+        <v>1</v>
+      </c>
+      <c r="O36" s="43">
+        <v>4</v>
+      </c>
+      <c r="P36" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>19</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -45815,18 +46039,32 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
+      <c r="F42" s="43">
+        <v>282</v>
+      </c>
+      <c r="G42" s="43">
+        <v>31</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
+      <c r="I42" s="43">
+        <v>6</v>
+      </c>
       <c r="J42" s="43"/>
       <c r="K42" s="43"/>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="N42" s="43">
+        <v>1</v>
+      </c>
+      <c r="O42" s="43">
+        <v>4</v>
+      </c>
+      <c r="P42" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>19</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -45868,7 +46106,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>2+7+1+71+2+224</f>
+        <v>307</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -45876,7 +46117,9 @@
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
+      <c r="C45" s="95">
+        <v>14</v>
+      </c>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
     </row>
@@ -46275,12 +46518,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -46290,14 +46539,20 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -46463,12 +46718,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>98</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -46478,25 +46739,37 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>2</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>1</v>
+      </c>
       <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65">
+        <v>15</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -46506,14 +46779,20 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>3</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -46915,17 +47194,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>79</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>425</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -47101,17 +47392,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>43</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>134</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -47129,17 +47432,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>36</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>20</v>
+      </c>
+      <c r="M32" s="28">
+        <v>291</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -47277,21 +47592,43 @@
       <c r="B36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="47"/>
+      <c r="C36" s="47">
+        <v>2</v>
+      </c>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
+      <c r="F36" s="43">
+        <v>302</v>
+      </c>
+      <c r="G36" s="43">
+        <v>3</v>
+      </c>
+      <c r="H36" s="43">
+        <v>3</v>
+      </c>
+      <c r="I36" s="43">
+        <v>46</v>
+      </c>
       <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
+      <c r="K36" s="43">
+        <v>12</v>
+      </c>
+      <c r="L36" s="43">
+        <v>2</v>
+      </c>
       <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="N36" s="43">
+        <v>64</v>
+      </c>
+      <c r="O36" s="43">
+        <v>8</v>
+      </c>
+      <c r="P36" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>22</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -47435,21 +47772,43 @@
       <c r="B42" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="47"/>
+      <c r="C42" s="47">
+        <v>2</v>
+      </c>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
+      <c r="F42" s="43">
+        <v>302</v>
+      </c>
+      <c r="G42" s="43">
+        <v>3</v>
+      </c>
+      <c r="H42" s="43">
+        <v>3</v>
+      </c>
+      <c r="I42" s="43">
+        <v>46</v>
+      </c>
       <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
+      <c r="K42" s="43">
+        <v>12</v>
+      </c>
+      <c r="L42" s="43">
+        <v>2</v>
+      </c>
       <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="N42" s="43">
+        <v>64</v>
+      </c>
+      <c r="O42" s="43">
+        <v>8</v>
+      </c>
+      <c r="P42" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>22</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -47491,7 +47850,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>1+1+15+3+36+1+20+291</f>
+        <v>368</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9DC409-CBA8-4CD2-904F-DC6F6BF71F29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B63271-AA29-40CE-B949-C6EAF00CBB2B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="109">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -389,6 +389,36 @@
   </si>
   <si>
     <t>5/20B</t>
+  </si>
+  <si>
+    <t>14/5B</t>
+  </si>
+  <si>
+    <t>1/5B</t>
+  </si>
+  <si>
+    <t>15/10B</t>
+  </si>
+  <si>
+    <t>15/20B</t>
+  </si>
+  <si>
+    <t>7/13B</t>
+  </si>
+  <si>
+    <t>8/7B</t>
+  </si>
+  <si>
+    <t>18/14B</t>
+  </si>
+  <si>
+    <t>23/14B</t>
+  </si>
+  <si>
+    <t>10/12B</t>
+  </si>
+  <si>
+    <t>12B</t>
   </si>
 </sst>
 </file>
@@ -3462,7 +3492,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -3831,12 +3862,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -3846,12 +3881,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>10</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>3</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
       <c r="X8" s="60"/>
       <c r="Y8" s="15"/>
     </row>
@@ -4019,12 +4060,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>5</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -4034,12 +4079,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>10</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="62"/>
       <c r="Y15" s="24"/>
     </row>
@@ -4047,12 +4098,16 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>105</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -4062,12 +4117,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>2</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>3</v>
+      </c>
       <c r="X16" s="63"/>
       <c r="Y16" s="29"/>
     </row>
@@ -4471,17 +4532,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>107</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>117</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>8</v>
+      </c>
+      <c r="M24" s="14">
+        <v>433</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>4</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -4657,17 +4728,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>108</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>2</v>
+      </c>
+      <c r="M31" s="23">
+        <v>74</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>1</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -4685,17 +4766,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>10</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>117</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>6</v>
+      </c>
+      <c r="M32" s="28">
+        <v>359</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>3</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -4833,21 +4924,47 @@
       <c r="B36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
+      <c r="C36" s="47">
+        <v>3</v>
+      </c>
+      <c r="D36" s="42">
+        <v>1</v>
+      </c>
+      <c r="E36" s="43">
+        <v>20</v>
+      </c>
+      <c r="F36" s="43">
+        <v>360</v>
+      </c>
+      <c r="G36" s="43">
+        <v>14</v>
+      </c>
+      <c r="H36" s="43">
+        <v>3</v>
+      </c>
+      <c r="I36" s="43">
+        <v>8</v>
+      </c>
       <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
+      <c r="K36" s="43">
+        <v>7</v>
+      </c>
+      <c r="L36" s="43">
+        <v>4</v>
+      </c>
       <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="N36" s="43">
+        <v>2</v>
+      </c>
+      <c r="O36" s="43">
+        <v>3</v>
+      </c>
+      <c r="P36" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>17</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -4991,21 +5108,47 @@
       <c r="B42" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="47"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
+      <c r="C42" s="47">
+        <v>3</v>
+      </c>
+      <c r="D42" s="42">
+        <v>1</v>
+      </c>
+      <c r="E42" s="43">
+        <v>20</v>
+      </c>
+      <c r="F42" s="43">
+        <v>360</v>
+      </c>
+      <c r="G42" s="43">
+        <v>14</v>
+      </c>
+      <c r="H42" s="43">
+        <v>3</v>
+      </c>
+      <c r="I42" s="43">
+        <v>8</v>
+      </c>
       <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
+      <c r="K42" s="43">
+        <v>7</v>
+      </c>
+      <c r="L42" s="43">
+        <v>4</v>
+      </c>
       <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="N42" s="43">
+        <v>2</v>
+      </c>
+      <c r="O42" s="43">
+        <v>3</v>
+      </c>
+      <c r="P42" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>17</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -5047,7 +5190,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>18+2+3+10+117+6+359+3</f>
+        <v>518</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -5055,7 +5201,10 @@
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
+      <c r="C45" s="95">
+        <f>14</f>
+        <v>14</v>
+      </c>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
     </row>
@@ -5085,7 +5234,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -5454,12 +5604,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -5469,14 +5627,20 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>10</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -5642,12 +5806,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22" t="s">
+        <v>93</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>2</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>100</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -5657,25 +5829,39 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>10</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="27">
+        <v>2</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>99</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -5685,14 +5871,20 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>0</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -6091,20 +6283,32 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>41</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>7</v>
+      </c>
+      <c r="M24" s="14">
+        <v>256</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -6277,20 +6481,32 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>1</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>41</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>7</v>
+      </c>
+      <c r="M31" s="23">
+        <v>30</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>96</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -6305,20 +6521,32 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>0</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>0</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>326</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -6459,18 +6687,30 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
+      <c r="F36" s="43">
+        <v>325</v>
+      </c>
+      <c r="G36" s="43">
+        <v>1</v>
+      </c>
+      <c r="H36" s="43">
+        <v>1</v>
+      </c>
       <c r="I36" s="43"/>
       <c r="J36" s="43"/>
       <c r="K36" s="43"/>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
       <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="O36" s="43">
+        <v>3</v>
+      </c>
+      <c r="P36" s="43">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>1</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -6617,18 +6857,30 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
+      <c r="F42" s="43">
+        <v>325</v>
+      </c>
+      <c r="G42" s="43">
+        <v>1</v>
+      </c>
+      <c r="H42" s="43">
+        <v>1</v>
+      </c>
       <c r="I42" s="43"/>
       <c r="J42" s="43"/>
       <c r="K42" s="43"/>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
       <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="O42" s="43">
+        <v>3</v>
+      </c>
+      <c r="P42" s="43">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>1</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -6670,7 +6922,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>2+14+326</f>
+        <v>342</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -6678,7 +6933,10 @@
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
+      <c r="C45" s="95">
+        <f>5</f>
+        <v>5</v>
+      </c>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
     </row>
@@ -7077,12 +7335,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>102</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -7092,14 +7360,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>10</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -7265,12 +7537,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>103</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -7280,25 +7562,39 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>10</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
+      <c r="D16" s="59">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>8</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>104</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -7308,14 +7604,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
       <c r="W16" s="57"/>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -7717,17 +8017,31 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="H24" s="14">
+        <v>64</v>
+      </c>
+      <c r="I24" s="14">
+        <v>1</v>
+      </c>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>15</v>
+      </c>
+      <c r="M24" s="14">
+        <v>350</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -7903,17 +8217,31 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="H31" s="23">
+        <v>35</v>
+      </c>
+      <c r="I31" s="23">
+        <v>0</v>
+      </c>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>15</v>
+      </c>
+      <c r="M31" s="23">
+        <v>80</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -7931,17 +8259,31 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="H32" s="28">
+        <v>29</v>
+      </c>
+      <c r="I32" s="28">
+        <v>1</v>
+      </c>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>270</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -8082,18 +8424,32 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
+      <c r="F36" s="43">
+        <v>297</v>
+      </c>
+      <c r="G36" s="43">
+        <v>2</v>
+      </c>
+      <c r="H36" s="43">
+        <v>2</v>
+      </c>
       <c r="I36" s="43"/>
       <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
+      <c r="K36" s="43">
+        <v>17</v>
+      </c>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
       <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="O36" s="43">
+        <v>5</v>
+      </c>
+      <c r="P36" s="43">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>6</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -8240,18 +8596,32 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
+      <c r="F42" s="43">
+        <v>297</v>
+      </c>
+      <c r="G42" s="43">
+        <v>2</v>
+      </c>
+      <c r="H42" s="43">
+        <v>2</v>
+      </c>
       <c r="I42" s="43"/>
       <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
+      <c r="K42" s="43">
+        <v>17</v>
+      </c>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
       <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="O42" s="43">
+        <v>5</v>
+      </c>
+      <c r="P42" s="43">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>6</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -8293,7 +8663,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>8+1+8+29+1+270</f>
+        <v>317</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -8301,7 +8674,10 @@
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
+      <c r="C45" s="95">
+        <f>7</f>
+        <v>7</v>
+      </c>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
     </row>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B63271-AA29-40CE-B949-C6EAF00CBB2B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224AF143-C539-4D8C-825D-4F84A9A2552A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -3492,7 +3492,9 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
@@ -6966,7 +6968,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224AF143-C539-4D8C-825D-4F84A9A2552A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFEEF54-428B-4DB2-AF7D-D2AEED3B206B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFEEF54-428B-4DB2-AF7D-D2AEED3B206B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DE0BC6-0F37-41EE-B8AC-DA32BFCCCDCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="12" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <sheet name="(5)" sheetId="1460" r:id="rId14"/>
     <sheet name="03-05 R1" sheetId="1461" r:id="rId15"/>
     <sheet name="03-05 R2" sheetId="1462" r:id="rId16"/>
-    <sheet name="03-05 R3" sheetId="1463" r:id="rId17"/>
+    <sheet name="03-05 R3 NO TRIP" sheetId="1463" r:id="rId17"/>
     <sheet name="(6)" sheetId="1464" r:id="rId18"/>
     <sheet name="03-06 R1" sheetId="1465" r:id="rId19"/>
     <sheet name="03-06 R2" sheetId="1466" r:id="rId20"/>
@@ -65,7 +65,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'03-04 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'03-05 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'03-05 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'03-05 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'03-05 R3 NO TRIP'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'03-06 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'03-06 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'03-06 R3'!$A$1:$V$44</definedName>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="111">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -419,6 +419,12 @@
   </si>
   <si>
     <t>12B</t>
+  </si>
+  <si>
+    <t>4/5B</t>
+  </si>
+  <si>
+    <t>11/5B</t>
   </si>
 </sst>
 </file>
@@ -10682,12 +10688,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -10697,12 +10707,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>10</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
       <c r="X8" s="60"/>
       <c r="Y8" s="15"/>
     </row>
@@ -10870,12 +10886,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>3</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -10885,12 +10905,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>8</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="62"/>
       <c r="Y15" s="24"/>
     </row>
@@ -10898,12 +10924,16 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65">
+        <v>10</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -10913,12 +10943,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>2</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>0</v>
+      </c>
       <c r="X16" s="63"/>
       <c r="Y16" s="29"/>
     </row>
@@ -11322,17 +11358,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>10</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>2</v>
+      </c>
+      <c r="M24" s="14">
+        <v>433</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>1</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -11508,17 +11554,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>108</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>2</v>
+      </c>
+      <c r="M31" s="23">
+        <v>56</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>1</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -11536,17 +11592,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>10</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>377</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -11687,18 +11753,34 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
+      <c r="F36" s="43">
+        <v>493</v>
+      </c>
+      <c r="G36" s="43">
+        <v>2</v>
+      </c>
+      <c r="H36" s="43">
+        <v>5</v>
+      </c>
       <c r="I36" s="43"/>
       <c r="J36" s="43"/>
       <c r="K36" s="43"/>
       <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="M36" s="43">
+        <v>1</v>
+      </c>
+      <c r="N36" s="43">
+        <v>6</v>
+      </c>
+      <c r="O36" s="43">
+        <v>5</v>
+      </c>
+      <c r="P36" s="43">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>18</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -11845,18 +11927,34 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
+      <c r="F42" s="43">
+        <v>493</v>
+      </c>
+      <c r="G42" s="43">
+        <v>2</v>
+      </c>
+      <c r="H42" s="43">
+        <v>5</v>
+      </c>
       <c r="I42" s="43"/>
       <c r="J42" s="43"/>
       <c r="K42" s="43"/>
       <c r="L42" s="43"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="M42" s="43">
+        <v>1</v>
+      </c>
+      <c r="N42" s="43">
+        <v>6</v>
+      </c>
+      <c r="O42" s="43">
+        <v>5</v>
+      </c>
+      <c r="P42" s="43">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>18</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -11898,7 +11996,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>10+2+1+10+377</f>
+        <v>400</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -12305,12 +12406,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>18</v>
+      </c>
+      <c r="F8" s="14">
+        <v>14</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>110</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -12320,14 +12429,22 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>10</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
+      <c r="U8" s="14">
+        <v>4</v>
+      </c>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -12493,12 +12610,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22" t="s">
+        <v>93</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>109</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -12508,25 +12633,41 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>10</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
+      <c r="U15" s="23">
+        <v>0</v>
+      </c>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
       <c r="D16" s="59"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>17</v>
+      </c>
+      <c r="F16" s="27">
+        <v>13</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65">
+        <v>7</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -12536,14 +12677,22 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
+      <c r="U16" s="28">
+        <v>4</v>
+      </c>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>2</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -12942,26 +13091,46 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>11</v>
+      </c>
       <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="E24" s="14">
+        <v>3</v>
+      </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="H24" s="14">
+        <v>41</v>
+      </c>
+      <c r="I24" s="14">
+        <v>6</v>
+      </c>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>7</v>
+      </c>
+      <c r="M24" s="14">
+        <v>331</v>
+      </c>
       <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="O24" s="14">
+        <v>4</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -13128,26 +13297,46 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
       <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="E31" s="23">
+        <v>0</v>
+      </c>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="H31" s="23">
+        <v>17</v>
+      </c>
+      <c r="I31" s="23">
+        <v>0</v>
+      </c>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>6</v>
+      </c>
+      <c r="M31" s="23">
+        <v>85</v>
+      </c>
       <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="O31" s="23">
+        <v>0</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>96</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="23">
+        <v>0</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="62"/>
       <c r="Y31" s="24"/>
@@ -13156,26 +13345,46 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>11</v>
+      </c>
       <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="E32" s="27">
+        <v>3</v>
+      </c>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="H32" s="28">
+        <v>24</v>
+      </c>
+      <c r="I32" s="28">
+        <v>6</v>
+      </c>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>1</v>
+      </c>
+      <c r="M32" s="28">
+        <v>246</v>
+      </c>
       <c r="N32" s="28"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="O32" s="23">
+        <v>4</v>
+      </c>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="V32" s="28">
+        <v>1</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="64"/>
       <c r="Y32" s="29"/>
@@ -13310,17 +13519,31 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
+      <c r="F36" s="43">
+        <v>304</v>
+      </c>
+      <c r="G36" s="43">
+        <v>1</v>
+      </c>
+      <c r="H36" s="43">
+        <v>5</v>
+      </c>
+      <c r="I36" s="43">
+        <v>3</v>
+      </c>
       <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
+      <c r="K36" s="43">
+        <v>2</v>
+      </c>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
       <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
+      <c r="O36" s="43">
+        <v>4</v>
+      </c>
+      <c r="P36" s="43">
+        <v>10</v>
+      </c>
       <c r="Q36" s="44"/>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
@@ -13468,17 +13691,31 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
+      <c r="F42" s="43">
+        <v>304</v>
+      </c>
+      <c r="G42" s="43">
+        <v>1</v>
+      </c>
+      <c r="H42" s="43">
+        <v>5</v>
+      </c>
+      <c r="I42" s="43">
+        <v>3</v>
+      </c>
       <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
+      <c r="K42" s="43">
+        <v>2</v>
+      </c>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
       <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
+      <c r="O42" s="43">
+        <v>4</v>
+      </c>
+      <c r="P42" s="43">
+        <v>10</v>
+      </c>
       <c r="Q42" s="44"/>
       <c r="R42" s="87" t="s">
         <v>54</v>
@@ -13521,7 +13758,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>17+13+7+4+2+11+3+24+6+1+246+4+1</f>
+        <v>339</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DE0BC6-0F37-41EE-B8AC-DA32BFCCCDCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FAD7B4-4E06-4B56-8DAC-F6BE869E89DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FAD7B4-4E06-4B56-8DAC-F6BE869E89DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D0BFBB-0594-4B1F-8A2F-3E1880659813}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -31,9 +31,9 @@
     <sheet name="03-05 R2" sheetId="1462" r:id="rId16"/>
     <sheet name="03-05 R3 NO TRIP" sheetId="1463" r:id="rId17"/>
     <sheet name="(6)" sheetId="1464" r:id="rId18"/>
-    <sheet name="03-06 R1" sheetId="1465" r:id="rId19"/>
-    <sheet name="03-06 R2" sheetId="1466" r:id="rId20"/>
-    <sheet name="03-06 R3" sheetId="1467" r:id="rId21"/>
+    <sheet name="03-06 R1 NO TRIP" sheetId="1467" r:id="rId19"/>
+    <sheet name="03-06 R2 NO TRIP" sheetId="1466" r:id="rId20"/>
+    <sheet name="03-06 R3" sheetId="1465" r:id="rId21"/>
     <sheet name="(7)" sheetId="1468" r:id="rId22"/>
     <sheet name="03-07 R1" sheetId="1469" r:id="rId23"/>
     <sheet name="03-07 R2" sheetId="1470" r:id="rId24"/>
@@ -66,9 +66,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'03-05 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'03-05 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'03-05 R3 NO TRIP'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'03-06 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'03-06 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="20">'03-06 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'03-06 R1 NO TRIP'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'03-06 R2 NO TRIP'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'03-06 R3'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'03-07 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'03-07 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="24">'03-07 R3'!$A$1:$V$44</definedName>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="113">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -425,6 +425,12 @@
   </si>
   <si>
     <t>11/5B</t>
+  </si>
+  <si>
+    <t>22/13b</t>
+  </si>
+  <si>
+    <t>13/13b</t>
   </si>
 </sst>
 </file>
@@ -17019,7 +17025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4C6D0A-3CC0-477D-A831-E3EA7809BFEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F9BD33-1BFF-4E7A-A164-05837058A447}">
   <dimension ref="B1:AA45"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18637,7 +18643,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21868,13 +21874,14 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F9BD33-1BFF-4E7A-A164-05837058A447}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4C6D0A-3CC0-477D-A831-E3EA7809BFEF}">
   <dimension ref="B1:AA45"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -22243,12 +22250,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>111</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -22258,14 +22271,20 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>10</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
       <c r="X8" s="60"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -22431,12 +22450,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>9</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -22446,25 +22471,37 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>10</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>4</v>
+      </c>
       <c r="X15" s="62"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="59"/>
+      <c r="C16" s="58">
+        <v>0</v>
+      </c>
+      <c r="D16" s="59">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="65"/>
+      <c r="H16" s="65" t="s">
+        <v>112</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="57"/>
@@ -22474,14 +22511,20 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="57"/>
+      <c r="W16" s="57">
+        <v>0</v>
+      </c>
       <c r="X16" s="63"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -22883,17 +22926,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>143</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>15</v>
+      </c>
+      <c r="M24" s="14">
+        <v>356</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -23069,17 +23124,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>32</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>5</v>
+      </c>
+      <c r="M31" s="23">
+        <v>1</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -23097,17 +23164,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>111</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>355</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -23248,18 +23327,32 @@
       <c r="C36" s="47"/>
       <c r="D36" s="42"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
+      <c r="F36" s="43">
+        <v>481</v>
+      </c>
+      <c r="G36" s="43">
+        <v>1</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
+      <c r="I36" s="43">
+        <v>7</v>
+      </c>
       <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
+      <c r="K36" s="43">
+        <v>2</v>
+      </c>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
       <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="44"/>
+      <c r="O36" s="43">
+        <v>4</v>
+      </c>
+      <c r="P36" s="43">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>9</v>
+      </c>
       <c r="R36" s="76"/>
       <c r="S36" s="66"/>
       <c r="T36" s="66"/>
@@ -23406,18 +23499,32 @@
       <c r="C42" s="47"/>
       <c r="D42" s="42"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
+      <c r="F42" s="43">
+        <v>481</v>
+      </c>
+      <c r="G42" s="43">
+        <v>1</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
+      <c r="I42" s="43">
+        <v>7</v>
+      </c>
       <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
+      <c r="K42" s="43">
+        <v>2</v>
+      </c>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
       <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
+      <c r="O42" s="43">
+        <v>4</v>
+      </c>
+      <c r="P42" s="43">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>9</v>
+      </c>
       <c r="R42" s="87" t="s">
         <v>54</v>
       </c>
@@ -23459,7 +23566,10 @@
       <c r="B44" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="95"/>
+      <c r="C44" s="95">
+        <f>13+111+10+355</f>
+        <v>489</v>
+      </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
     </row>
@@ -23467,7 +23577,10 @@
       <c r="B45" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="95"/>
+      <c r="C45" s="95">
+        <f>13</f>
+        <v>13</v>
+      </c>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
     </row>
@@ -23486,7 +23599,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D0BFBB-0594-4B1F-8A2F-3E1880659813}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A927EF-4BEA-4D8A-8343-D5EF73AADB62}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>

--- a/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/CSR MONTH OF MARCH 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hu4fxw\GBDS\GBDS MARCH FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FDA8EE-F8B9-4F6B-AC25-8F550373A678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EC7434-0F41-4323-BFBF-CF9EF90AED36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="15" activeTab="24" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
@@ -87,9 +87,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -449,8 +449,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
@@ -1058,8 +1058,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="90">
@@ -1160,10 +1160,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1175,7 +1175,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1276,7 +1276,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1360,7 +1360,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="DSSR"/>
@@ -1584,9 +1584,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1624,7 +1624,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1730,7 +1730,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1872,7 +1872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
